--- a/SPDR/spdr.xlsx
+++ b/SPDR/spdr.xlsx
@@ -1,24 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7c741cee80ec8cf3/Financieel/IndexFondsenOnderzoek/KeuzeWelkIndexFonds/OnderzoekPerFonds/SPDR/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="721" documentId="8_{F0B8999D-9BF9-463A-A515-6683C4D9B0FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4353CEE4-DC1A-4AC7-BD02-B3C3CA580FB6}"/>
+  <xr:revisionPtr revIDLastSave="959" documentId="8_{F0B8999D-9BF9-463A-A515-6683C4D9B0FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1509E12E-F128-46CC-A053-B54BC6B4FDE4}"/>
   <bookViews>
-    <workbookView xWindow="26445" yWindow="3750" windowWidth="24360" windowHeight="15930" activeTab="3" xr2:uid="{CB9E69B2-3CC2-4CB8-BB0A-750BABFBC08D}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="5" xr2:uid="{CB9E69B2-3CC2-4CB8-BB0A-750BABFBC08D}"/>
   </bookViews>
   <sheets>
     <sheet name="SWRD" sheetId="2" r:id="rId1"/>
     <sheet name="ZPRV" sheetId="1" r:id="rId2"/>
     <sheet name="ZPRX" sheetId="5" r:id="rId3"/>
-    <sheet name="TrackingDiff" sheetId="3" r:id="rId4"/>
+    <sheet name="SPYI" sheetId="6" r:id="rId4"/>
+    <sheet name="SPYY" sheetId="7" r:id="rId5"/>
+    <sheet name="TrackingDiff" sheetId="3" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -42,7 +44,7 @@
     <author>Gerben</author>
   </authors>
   <commentList>
-    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{037CF0A5-8A77-4058-828B-8C964D69D56D}">
+    <comment ref="N1" authorId="0" shapeId="0" xr:uid="{037CF0A5-8A77-4058-828B-8C964D69D56D}">
       <text>
         <r>
           <rPr>
@@ -66,7 +68,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{D86604A5-7F37-43DE-A45A-81031088F21C}">
+    <comment ref="O1" authorId="0" shapeId="0" xr:uid="{D86604A5-7F37-43DE-A45A-81031088F21C}">
       <text>
         <r>
           <rPr>
@@ -95,10 +97,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="44">
-  <si>
-    <t>financial year ended 31 March 2020</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="59">
   <si>
     <t>TER</t>
   </si>
@@ -199,9 +198,6 @@
     <t>Average costs in the past</t>
   </si>
   <si>
-    <t>financial year ended 31 March 2021</t>
-  </si>
-  <si>
     <t>SWRD</t>
   </si>
   <si>
@@ -227,6 +223,57 @@
   </si>
   <si>
     <t>MSCI USA Small Cap Value Weighted</t>
+  </si>
+  <si>
+    <t>TER reported</t>
+  </si>
+  <si>
+    <t>Net asset value end of year</t>
+  </si>
+  <si>
+    <t>Average assets via management fee</t>
+  </si>
+  <si>
+    <t>Securities lending income</t>
+  </si>
+  <si>
+    <t>% lending income</t>
+  </si>
+  <si>
+    <t>KID % transaction costs</t>
+  </si>
+  <si>
+    <t>Estimated future costs</t>
+  </si>
+  <si>
+    <t>Lending</t>
+  </si>
+  <si>
+    <t>SPDR MSCI All Country World Investable Market UCITS ETF Acc (SPYI)</t>
+  </si>
+  <si>
+    <t>financial year ended 31 March</t>
+  </si>
+  <si>
+    <t>SPDR MSCI All Country World UCITS ETF Acc (SPYY)</t>
+  </si>
+  <si>
+    <t>0,40% to 0,12%</t>
+  </si>
+  <si>
+    <t>The TER of SPDR MSCI ACWI IMI UCITS ETF changed from 0.40% to 0.17% effective 3 April 2023.</t>
+  </si>
+  <si>
+    <t>TER reductions became effective as at 1 August 2024</t>
+  </si>
+  <si>
+    <t>SPYI</t>
+  </si>
+  <si>
+    <t>SPYY</t>
+  </si>
+  <si>
+    <t>Gross index</t>
   </si>
 </sst>
 </file>
@@ -326,7 +373,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -350,12 +397,23 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="Komma" xfId="1" builtinId="3"/>
-    <cellStyle name="Procent" xfId="2" builtinId="5"/>
-    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
-    <cellStyle name="Valuta" xfId="3" builtinId="4"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="3" builtinId="4"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -370,10 +428,14 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Kantoorthema">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -411,7 +473,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -517,7 +579,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -659,7 +721,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -679,12 +741,12 @@
   <sheetData>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -702,15 +764,15 @@
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B5" s="6">
         <v>318392294</v>
@@ -728,7 +790,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" s="6"/>
       <c r="C6" s="6">
@@ -744,7 +806,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B7" s="2">
         <v>1.1999999999999999E-3</v>
@@ -766,7 +828,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" s="6"/>
       <c r="C8" s="6">
@@ -785,7 +847,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B10" s="6">
         <v>1004942</v>
@@ -803,7 +865,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B11" s="6">
         <v>135108</v>
@@ -821,7 +883,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B12" s="13">
         <f>B11/B10</f>
@@ -844,7 +906,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C13" s="2">
         <f>C11/C8</f>
@@ -866,7 +928,7 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B16" s="6">
         <v>144398</v>
@@ -884,7 +946,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C17" s="2">
         <f>C16/C8</f>
@@ -906,7 +968,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" s="2">
         <f>G7+G13+G17</f>
@@ -915,16 +977,16 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B21" s="4">
-        <f>TrackingDiff!K5/100</f>
+        <f>TrackingDiff!N5/100</f>
         <v>5.3000000000000026E-3</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B22" s="2">
         <f>B20-B21</f>
@@ -1009,7 +1071,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2">
@@ -1042,7 +1104,7 @@
   <sheetData>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B2" s="15"/>
       <c r="C2" s="15"/>
@@ -1054,12 +1116,12 @@
       <c r="I2" s="15"/>
       <c r="J2" s="15"/>
       <c r="L2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -1086,15 +1148,15 @@
         <v>2022</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L4" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B5" s="3">
         <v>16620593</v>
@@ -1118,12 +1180,12 @@
         <v>350309639</v>
       </c>
       <c r="L5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B6" s="2">
         <v>3.0000000000000001E-3</v>
@@ -1148,12 +1210,12 @@
       </c>
       <c r="J6" s="2"/>
       <c r="L6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B7" s="3">
         <v>227317</v>
@@ -1180,7 +1242,7 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" s="3">
         <f t="shared" ref="B8" si="0">B7/B6</f>
@@ -1217,7 +1279,7 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B10" s="3">
         <v>1395145</v>
@@ -1244,7 +1306,7 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B11" s="3">
         <v>278674</v>
@@ -1271,7 +1333,7 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B12" s="16">
         <f>B11/B10</f>
@@ -1308,7 +1370,7 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B13" s="4">
         <f>B10/B8</f>
@@ -1345,7 +1407,7 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B14" s="4">
         <f>B11/B8</f>
@@ -1385,7 +1447,7 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B16" s="3">
         <v>20213</v>
@@ -1412,7 +1474,7 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B17" s="17">
         <f>B16/B8</f>
@@ -1449,7 +1511,7 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G18" s="2">
         <v>0.20169999999999999</v>
@@ -1460,7 +1522,7 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B20" s="2">
         <f>H6+J14+J17</f>
@@ -1469,7 +1531,7 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B25" s="1">
         <f>B4</f>
@@ -1604,7 +1666,7 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B29" s="2">
         <f>SUM(B26:B28)</f>
@@ -1657,7 +1719,7 @@
   <sheetData>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B2" s="15"/>
       <c r="C2" s="15"/>
@@ -1669,12 +1731,12 @@
       <c r="I2" s="15"/>
       <c r="J2" s="15"/>
       <c r="L2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -1702,15 +1764,15 @@
       </c>
       <c r="I4" s="1"/>
       <c r="J4" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L4" t="s">
-        <v>0</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B5" s="3">
         <v>29596852</v>
@@ -1738,7 +1800,7 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B6" s="2">
         <v>3.0000000000000001E-3</v>
@@ -1766,7 +1828,7 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B7" s="3">
         <v>260185</v>
@@ -1794,7 +1856,7 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" s="3">
         <f t="shared" ref="B8" si="0">B7/B6</f>
@@ -1829,7 +1891,7 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B10" s="3">
         <v>2327973</v>
@@ -1857,7 +1919,7 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B11" s="3">
         <v>137864</v>
@@ -1885,7 +1947,7 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B12" s="4">
         <f>B11/B10</f>
@@ -1923,7 +1985,7 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B13" s="4">
         <f>B10/B8</f>
@@ -1960,7 +2022,7 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B14" s="4">
         <f>B11/B8</f>
@@ -2000,7 +2062,7 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B16" s="3">
         <v>131088</v>
@@ -2028,7 +2090,7 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B17" s="4">
         <f t="shared" ref="B17:E17" si="10">B16/B8</f>
@@ -2066,7 +2128,7 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
@@ -2083,7 +2145,7 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B20" s="2">
         <f>G6+J14+J17</f>
@@ -2095,7 +2157,7 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B25" s="1">
         <f>B4</f>
@@ -2230,7 +2292,7 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B29" s="2">
         <f>SUM(B26:B28)</f>
@@ -2272,14 +2334,838 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08FC4ABB-EB76-42C9-BCD5-AAAD094BB644}">
+  <dimension ref="A2:N37"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="36.42578125" customWidth="1"/>
+    <col min="2" max="7" width="17.7109375" customWidth="1"/>
+    <col min="8" max="8" width="13.28515625" customWidth="1"/>
+    <col min="12" max="12" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="I2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B4" s="1">
+        <v>2020</v>
+      </c>
+      <c r="C4" s="1">
+        <v>2021</v>
+      </c>
+      <c r="D4" s="1">
+        <v>2022</v>
+      </c>
+      <c r="E4" s="1">
+        <v>2023</v>
+      </c>
+      <c r="F4" s="1">
+        <v>2024</v>
+      </c>
+      <c r="G4" s="1">
+        <v>2025</v>
+      </c>
+      <c r="I4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="20">
+        <v>1844639</v>
+      </c>
+      <c r="F5" s="20">
+        <v>1345720</v>
+      </c>
+      <c r="G5" s="20">
+        <v>3442955</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" s="21">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="F6" s="21">
+        <v>1.6999999999999999E-3</v>
+      </c>
+      <c r="G6" s="21">
+        <v>1.6999999999999999E-3</v>
+      </c>
+      <c r="I6" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" s="19">
+        <v>524231887</v>
+      </c>
+      <c r="F7" s="19">
+        <v>1328722329</v>
+      </c>
+      <c r="G7" s="19">
+        <v>2748852311</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" s="20">
+        <f>E5/E6</f>
+        <v>461159750</v>
+      </c>
+      <c r="F8" s="20">
+        <f>F5/F6</f>
+        <v>791600000</v>
+      </c>
+      <c r="G8" s="20">
+        <f>G5/G6</f>
+        <v>2025267647.0588236</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E9" s="22"/>
+      <c r="F9" s="22"/>
+      <c r="G9" s="22"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="19">
+        <v>3812795</v>
+      </c>
+      <c r="C10" s="19">
+        <v>5004773</v>
+      </c>
+      <c r="D10" s="19">
+        <v>8491140</v>
+      </c>
+      <c r="E10" s="19">
+        <v>11061893</v>
+      </c>
+      <c r="F10" s="19">
+        <v>17303517</v>
+      </c>
+      <c r="G10" s="19">
+        <v>39985661</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="19">
+        <v>492580</v>
+      </c>
+      <c r="C11" s="19">
+        <v>668932</v>
+      </c>
+      <c r="D11" s="19">
+        <v>1076957</v>
+      </c>
+      <c r="E11" s="19">
+        <v>1399652</v>
+      </c>
+      <c r="F11" s="19">
+        <v>2224854</v>
+      </c>
+      <c r="G11" s="19">
+        <v>5092103</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="16">
+        <f>B11/B10</f>
+        <v>0.12919131503267289</v>
+      </c>
+      <c r="C12" s="16">
+        <f t="shared" ref="C12:G12" si="0">C11/C10</f>
+        <v>0.13365880930064161</v>
+      </c>
+      <c r="D12" s="16">
+        <f t="shared" si="0"/>
+        <v>0.12683302830950849</v>
+      </c>
+      <c r="E12" s="16">
+        <f t="shared" si="0"/>
+        <v>0.12652915735127795</v>
+      </c>
+      <c r="F12" s="16">
+        <f t="shared" si="0"/>
+        <v>0.12857813819005698</v>
+      </c>
+      <c r="G12" s="16">
+        <f t="shared" si="0"/>
+        <v>0.12734822615537106</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>45</v>
+      </c>
+      <c r="E14" s="19">
+        <v>0</v>
+      </c>
+      <c r="F14" s="19">
+        <v>97271</v>
+      </c>
+      <c r="G14" s="20">
+        <v>429604</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15" s="23">
+        <f>E14/E8</f>
+        <v>0</v>
+      </c>
+      <c r="F15" s="23">
+        <f>F14/F8</f>
+        <v>1.2287897928246589E-4</v>
+      </c>
+      <c r="G15" s="23">
+        <f>G14/G8</f>
+        <v>2.1212208698632423E-4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="20"/>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="E17" s="22"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="22"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>47</v>
+      </c>
+      <c r="G18" s="2">
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="E20" s="2"/>
+      <c r="G20" s="24"/>
+      <c r="L20" s="2"/>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="L21" s="25"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>49</v>
+      </c>
+      <c r="E22" s="26">
+        <f>AVERAGE(F15:G15)</f>
+        <v>1.6750053313439506E-4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="H23" s="26"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="24"/>
+      <c r="H24" s="26"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="H25" s="26"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="H26" s="26"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="E27" s="26"/>
+      <c r="F27" s="24"/>
+      <c r="G27" s="24"/>
+      <c r="H27" s="26"/>
+      <c r="L27" s="4"/>
+      <c r="N27" s="27"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="E28" s="26"/>
+      <c r="F28" s="24"/>
+      <c r="G28" s="24"/>
+      <c r="H28" s="26"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F29" s="24"/>
+      <c r="G29" s="24"/>
+      <c r="H29" s="26"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="E30" s="26"/>
+      <c r="F30" s="24"/>
+      <c r="G30" s="24"/>
+      <c r="H30" s="26"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="28"/>
+      <c r="F31" s="24"/>
+      <c r="G31" s="24"/>
+      <c r="H31" s="26"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="24"/>
+      <c r="G32" s="24"/>
+      <c r="H32" s="26"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="1"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="24"/>
+      <c r="G33" s="24"/>
+      <c r="H33" s="26"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="1"/>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="24"/>
+      <c r="G34" s="24"/>
+      <c r="H34" s="26"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="1"/>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="24"/>
+      <c r="G35" s="24"/>
+      <c r="H35" s="26"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="1"/>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="24"/>
+      <c r="G36" s="24"/>
+      <c r="H36" s="26"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="1"/>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="24"/>
+      <c r="G37" s="24"/>
+      <c r="H37" s="26"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56730AE6-CAC9-4FBF-9A69-3BEA9518C12B}">
+  <dimension ref="A2:P37"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="36.42578125" customWidth="1"/>
+    <col min="2" max="8" width="17.7109375" customWidth="1"/>
+    <col min="9" max="10" width="13.28515625" customWidth="1"/>
+    <col min="14" max="14" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B4" s="1">
+        <v>2020</v>
+      </c>
+      <c r="C4" s="1">
+        <v>2021</v>
+      </c>
+      <c r="D4" s="1">
+        <v>2022</v>
+      </c>
+      <c r="E4" s="1">
+        <v>2023</v>
+      </c>
+      <c r="F4" s="1">
+        <v>2024</v>
+      </c>
+      <c r="G4" s="1">
+        <v>2025</v>
+      </c>
+      <c r="H4" s="1"/>
+      <c r="K4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="19">
+        <v>10742916</v>
+      </c>
+      <c r="F5" s="19">
+        <v>11946806</v>
+      </c>
+      <c r="G5" s="20">
+        <v>7927976</v>
+      </c>
+      <c r="H5" s="20"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" s="21">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="F6" s="4">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="G6" s="21">
+        <f>((4/12)*0.4%)+((8/12)*0.12%)</f>
+        <v>2.1333333333333334E-3</v>
+      </c>
+      <c r="H6" s="21"/>
+      <c r="K6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" s="19">
+        <v>2636854813</v>
+      </c>
+      <c r="F7" s="19">
+        <v>3411579317</v>
+      </c>
+      <c r="G7" s="19">
+        <v>4726963005</v>
+      </c>
+      <c r="H7" s="19"/>
+      <c r="K7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" s="20">
+        <f>E5/E6</f>
+        <v>2685729000</v>
+      </c>
+      <c r="F8" s="20">
+        <f t="shared" ref="F8:G8" si="0">F5/F6</f>
+        <v>2986701500</v>
+      </c>
+      <c r="G8" s="20">
+        <f t="shared" si="0"/>
+        <v>3716238750</v>
+      </c>
+      <c r="H8" s="20"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E9" s="22"/>
+      <c r="F9" s="22"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="22"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="19">
+        <v>39832319</v>
+      </c>
+      <c r="C10" s="19">
+        <v>41997255</v>
+      </c>
+      <c r="D10" s="19">
+        <v>62124429</v>
+      </c>
+      <c r="E10" s="19">
+        <v>61896624</v>
+      </c>
+      <c r="F10" s="19">
+        <v>63358943</v>
+      </c>
+      <c r="G10" s="19">
+        <v>73093049</v>
+      </c>
+      <c r="H10" s="19"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="19">
+        <v>4995505</v>
+      </c>
+      <c r="C11" s="19">
+        <v>5562292</v>
+      </c>
+      <c r="D11" s="19">
+        <v>7475182</v>
+      </c>
+      <c r="E11" s="19">
+        <v>7741026</v>
+      </c>
+      <c r="F11" s="19">
+        <v>7872056</v>
+      </c>
+      <c r="G11" s="19">
+        <v>9147920</v>
+      </c>
+      <c r="H11" s="19"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="16">
+        <f>B11/B10</f>
+        <v>0.12541336094441299</v>
+      </c>
+      <c r="C12" s="16">
+        <f t="shared" ref="C12:G12" si="1">C11/C10</f>
+        <v>0.13244417998271554</v>
+      </c>
+      <c r="D12" s="16">
+        <f t="shared" si="1"/>
+        <v>0.12032596710063927</v>
+      </c>
+      <c r="E12" s="16">
+        <f t="shared" si="1"/>
+        <v>0.12506378376953159</v>
+      </c>
+      <c r="F12" s="16">
+        <f t="shared" si="1"/>
+        <v>0.12424538079809823</v>
+      </c>
+      <c r="G12" s="16">
+        <f t="shared" si="1"/>
+        <v>0.12515444526058833</v>
+      </c>
+      <c r="H12" s="16"/>
+      <c r="I12" s="29">
+        <f>AVERAGE(B12:G12)</f>
+        <v>0.12544118630933099</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="20"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>45</v>
+      </c>
+      <c r="E14" s="19">
+        <v>0</v>
+      </c>
+      <c r="F14" s="19">
+        <v>211843</v>
+      </c>
+      <c r="G14" s="20">
+        <v>707668</v>
+      </c>
+      <c r="H14" s="20"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15" s="23">
+        <f>E14/E8</f>
+        <v>0</v>
+      </c>
+      <c r="F15" s="23">
+        <f>F14/F8</f>
+        <v>7.0928748654661332E-5</v>
+      </c>
+      <c r="G15" s="23">
+        <f>G14/G8</f>
+        <v>1.9042587078131081E-4</v>
+      </c>
+      <c r="H15" s="23"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="E17" s="22"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="22"/>
+      <c r="H17" s="22"/>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>47</v>
+      </c>
+      <c r="G18" s="2">
+        <v>0</v>
+      </c>
+      <c r="H18" s="2"/>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="E20" s="2"/>
+      <c r="G20" s="24"/>
+      <c r="H20" s="24"/>
+      <c r="N20" s="2"/>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="N21" s="25"/>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>49</v>
+      </c>
+      <c r="E22" s="26">
+        <f>AVERAGE(F15:G15)</f>
+        <v>1.3067730971798606E-4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="I23" s="26"/>
+      <c r="J23" s="26"/>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="24"/>
+      <c r="I24" s="26"/>
+      <c r="J24" s="26"/>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="I25" s="26"/>
+      <c r="J25" s="26"/>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="I26" s="26"/>
+      <c r="J26" s="26"/>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="E27" s="26"/>
+      <c r="F27" s="24"/>
+      <c r="G27" s="24"/>
+      <c r="H27" s="24"/>
+      <c r="I27" s="26"/>
+      <c r="J27" s="26"/>
+      <c r="N27" s="4"/>
+      <c r="P27" s="27"/>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="E28" s="26"/>
+      <c r="F28" s="24"/>
+      <c r="G28" s="24"/>
+      <c r="H28" s="24"/>
+      <c r="I28" s="26"/>
+      <c r="J28" s="26"/>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="F29" s="24"/>
+      <c r="G29" s="24"/>
+      <c r="H29" s="24"/>
+      <c r="I29" s="26"/>
+      <c r="J29" s="26"/>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="E30" s="26"/>
+      <c r="F30" s="24"/>
+      <c r="G30" s="24"/>
+      <c r="H30" s="24"/>
+      <c r="I30" s="26"/>
+      <c r="J30" s="26"/>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="28"/>
+      <c r="F31" s="24"/>
+      <c r="G31" s="24"/>
+      <c r="H31" s="24"/>
+      <c r="I31" s="26"/>
+      <c r="J31" s="26"/>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="24"/>
+      <c r="G32" s="24"/>
+      <c r="H32" s="24"/>
+      <c r="I32" s="26"/>
+      <c r="J32" s="26"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="1"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="24"/>
+      <c r="G33" s="24"/>
+      <c r="H33" s="24"/>
+      <c r="I33" s="26"/>
+      <c r="J33" s="26"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="1"/>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="24"/>
+      <c r="G34" s="24"/>
+      <c r="H34" s="24"/>
+      <c r="I34" s="26"/>
+      <c r="J34" s="26"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" s="1"/>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="24"/>
+      <c r="G35" s="24"/>
+      <c r="H35" s="24"/>
+      <c r="I35" s="26"/>
+      <c r="J35" s="26"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="1"/>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="24"/>
+      <c r="G36" s="24"/>
+      <c r="H36" s="24"/>
+      <c r="I36" s="26"/>
+      <c r="J36" s="26"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="1"/>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="24"/>
+      <c r="G37" s="24"/>
+      <c r="H37" s="24"/>
+      <c r="I37" s="26"/>
+      <c r="J37" s="26"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{458D1CFB-D8C8-403E-BC0B-3F57B3C7A83B}">
-  <dimension ref="B1:L17"/>
+  <dimension ref="B1:O27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="44.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C1" s="1">
         <v>2016</v>
       </c>
@@ -2301,17 +3187,26 @@
       <c r="I1" s="8">
         <v>2022</v>
       </c>
-      <c r="J1" s="9"/>
-      <c r="K1" s="8" t="s">
+      <c r="J1" s="8">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="8">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="8">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="9"/>
+      <c r="N1" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="O1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B2" s="8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C2" s="10"/>
       <c r="D2" s="10"/>
@@ -2327,10 +3222,13 @@
       <c r="J2" s="9"/>
       <c r="K2" s="9"/>
       <c r="L2" s="9"/>
-    </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
+    </row>
+    <row r="3" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B3" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C3" s="10"/>
       <c r="D3" s="10"/>
@@ -2344,12 +3242,15 @@
       </c>
       <c r="I3" s="9"/>
       <c r="J3" s="9"/>
-      <c r="K3" s="11"/>
-      <c r="L3" s="11"/>
-    </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+      <c r="N3" s="11"/>
+      <c r="O3" s="11"/>
+    </row>
+    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B4" s="8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C4" s="12"/>
       <c r="D4" s="12"/>
@@ -2363,12 +3264,15 @@
       </c>
       <c r="I4" s="9"/>
       <c r="J4" s="9"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-    </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="11"/>
+      <c r="O4" s="11"/>
+    </row>
+    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B5" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5" s="10"/>
       <c r="D5" s="10"/>
@@ -2384,15 +3288,18 @@
       </c>
       <c r="I5" s="10"/>
       <c r="J5" s="9"/>
-      <c r="K5" s="11">
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
+      <c r="N5" s="11">
         <f>AVERAGE(G5:H5)</f>
         <v>0.53000000000000025</v>
       </c>
-      <c r="L5" s="11"/>
-    </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="O5" s="11"/>
+    </row>
+    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B6" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C6" s="10"/>
       <c r="D6" s="10"/>
@@ -2408,15 +3315,18 @@
       </c>
       <c r="I6" s="10"/>
       <c r="J6" s="9"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="11">
+      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="11"/>
+      <c r="O6" s="11">
         <f>AVERAGE(G6:H6)</f>
         <v>3.5000000000000142E-2</v>
       </c>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B9" s="8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C9" s="18">
         <v>25.83</v>
@@ -2440,9 +3350,9 @@
         <v>-10.23</v>
       </c>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B10" s="8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C10">
         <v>27.3</v>
@@ -2466,9 +3376,9 @@
         <v>-9.67</v>
       </c>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B11" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C11" s="18">
         <f t="shared" ref="C11:H11" si="2">C10-C9</f>
@@ -2498,23 +3408,23 @@
         <f>I10-I9</f>
         <v>0.5600000000000005</v>
       </c>
-      <c r="K11" s="18">
+      <c r="N11" s="18">
         <f>AVERAGE(C11:I11)</f>
         <v>0.91857142857142926</v>
       </c>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="K12" s="18"/>
-    </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="K13" s="18"/>
-    </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="K14" s="18"/>
-    </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="N12" s="18"/>
+    </row>
+    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="N13" s="18"/>
+    </row>
+    <row r="14" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="N14" s="18"/>
+    </row>
+    <row r="15" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B15" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C15">
         <v>3.99</v>
@@ -2537,11 +3447,11 @@
       <c r="I15">
         <v>-14.27</v>
       </c>
-      <c r="K15" s="18"/>
-    </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="N15" s="18"/>
+    </row>
+    <row r="16" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B16" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C16">
         <v>4.33</v>
@@ -2564,11 +3474,11 @@
       <c r="I16">
         <v>-14.06</v>
       </c>
-      <c r="K16" s="18"/>
-    </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="N16" s="18"/>
+    </row>
+    <row r="17" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B17" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C17" s="18">
         <f t="shared" ref="C17" si="3">C16-C15</f>
@@ -2579,7 +3489,7 @@
         <v>1.5600000000000005</v>
       </c>
       <c r="E17" s="18">
-        <f t="shared" ref="C17:H17" si="5">E16-E15</f>
+        <f t="shared" ref="E17:H17" si="5">E16-E15</f>
         <v>0.33000000000000185</v>
       </c>
       <c r="F17" s="18">
@@ -2598,9 +3508,161 @@
         <f>I16-I15</f>
         <v>0.20999999999999908</v>
       </c>
-      <c r="K17" s="18">
+      <c r="N17" s="18">
         <f>AVERAGE(C17:I17)</f>
         <v>0.69714285714285762</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B18" s="8"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="18"/>
+      <c r="H18" s="18"/>
+      <c r="I18" s="18"/>
+      <c r="N18" s="18"/>
+    </row>
+    <row r="20" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B20" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G20">
+        <v>15.35</v>
+      </c>
+      <c r="H20">
+        <v>18.25</v>
+      </c>
+      <c r="I20">
+        <v>-17.52</v>
+      </c>
+      <c r="J20">
+        <v>21.1</v>
+      </c>
+      <c r="K20">
+        <v>16.13</v>
+      </c>
+    </row>
+    <row r="21" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B21" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G21">
+        <v>16.809999999999999</v>
+      </c>
+      <c r="H21">
+        <v>18.71</v>
+      </c>
+      <c r="I21">
+        <v>-18</v>
+      </c>
+      <c r="J21">
+        <v>22.18</v>
+      </c>
+      <c r="K21">
+        <v>16.89</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B22" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G22">
+        <f>G21-G20</f>
+        <v>1.4599999999999991</v>
+      </c>
+      <c r="H22">
+        <f t="shared" ref="H22:K22" si="6">H21-H20</f>
+        <v>0.46000000000000085</v>
+      </c>
+      <c r="I22">
+        <f t="shared" si="6"/>
+        <v>-0.48000000000000043</v>
+      </c>
+      <c r="J22">
+        <f t="shared" si="6"/>
+        <v>1.0799999999999983</v>
+      </c>
+      <c r="K22">
+        <f t="shared" si="6"/>
+        <v>0.76000000000000156</v>
+      </c>
+      <c r="N22" s="18">
+        <f>AVERAGE(G22:K22)</f>
+        <v>0.65599999999999992</v>
+      </c>
+    </row>
+    <row r="23" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B23" s="8"/>
+    </row>
+    <row r="25" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B25" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G25">
+        <v>15.7</v>
+      </c>
+      <c r="H25">
+        <v>18.59</v>
+      </c>
+      <c r="I25">
+        <v>-18.3</v>
+      </c>
+      <c r="J25">
+        <v>22.01</v>
+      </c>
+      <c r="K25">
+        <v>17.36</v>
+      </c>
+    </row>
+    <row r="26" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B26" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G26">
+        <v>16.61</v>
+      </c>
+      <c r="H26">
+        <v>18.82</v>
+      </c>
+      <c r="I26">
+        <v>-18.12</v>
+      </c>
+      <c r="J26">
+        <v>22.56</v>
+      </c>
+      <c r="K26">
+        <v>17.79</v>
+      </c>
+    </row>
+    <row r="27" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B27" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G27">
+        <f>G26-G25</f>
+        <v>0.91000000000000014</v>
+      </c>
+      <c r="H27">
+        <f t="shared" ref="H27:K27" si="7">H26-H25</f>
+        <v>0.23000000000000043</v>
+      </c>
+      <c r="I27">
+        <f t="shared" si="7"/>
+        <v>0.17999999999999972</v>
+      </c>
+      <c r="J27">
+        <f t="shared" si="7"/>
+        <v>0.54999999999999716</v>
+      </c>
+      <c r="K27">
+        <f t="shared" si="7"/>
+        <v>0.42999999999999972</v>
+      </c>
+      <c r="N27">
+        <f>AVERAGE(G27:K27)</f>
+        <v>0.45999999999999941</v>
       </c>
     </row>
   </sheetData>

--- a/SPDR/spdr.xlsx
+++ b/SPDR/spdr.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7c741cee80ec8cf3/Financieel/IndexFondsenOnderzoek/KeuzeWelkIndexFonds/OnderzoekPerFonds/SPDR/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="959" documentId="8_{F0B8999D-9BF9-463A-A515-6683C4D9B0FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1509E12E-F128-46CC-A053-B54BC6B4FDE4}"/>
+  <xr:revisionPtr revIDLastSave="991" documentId="8_{F0B8999D-9BF9-463A-A515-6683C4D9B0FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0450E012-EABD-4E0B-B330-9DA5B3CD00D3}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="5" xr2:uid="{CB9E69B2-3CC2-4CB8-BB0A-750BABFBC08D}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="1" xr2:uid="{CB9E69B2-3CC2-4CB8-BB0A-750BABFBC08D}"/>
   </bookViews>
   <sheets>
     <sheet name="SWRD" sheetId="2" r:id="rId1"/>
@@ -97,7 +97,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="60">
   <si>
     <t>TER</t>
   </si>
@@ -274,6 +274,9 @@
   </si>
   <si>
     <t>Gross index</t>
+  </si>
+  <si>
+    <t>Net index</t>
   </si>
 </sst>
 </file>
@@ -426,10 +429,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3159,7 +3158,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{458D1CFB-D8C8-403E-BC0B-3F57B3C7A83B}">
-  <dimension ref="B1:O27"/>
+  <dimension ref="B1:O29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="44.42578125" customWidth="1"/>
@@ -3476,7 +3475,7 @@
       </c>
       <c r="N16" s="18"/>
     </row>
-    <row r="17" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B17" s="8" t="s">
         <v>11</v>
       </c>
@@ -3513,7 +3512,7 @@
         <v>0.69714285714285762</v>
       </c>
     </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B18" s="8"/>
       <c r="C18" s="18"/>
       <c r="D18" s="18"/>
@@ -3524,7 +3523,7 @@
       <c r="I18" s="18"/>
       <c r="N18" s="18"/>
     </row>
-    <row r="20" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B20" s="1" t="s">
         <v>56</v>
       </c>
@@ -3544,7 +3543,7 @@
         <v>16.13</v>
       </c>
     </row>
-    <row r="21" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
         <v>58</v>
       </c>
@@ -3564,7 +3563,7 @@
         <v>16.89</v>
       </c>
     </row>
-    <row r="22" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B22" s="8" t="s">
         <v>11</v>
       </c>
@@ -3593,10 +3592,10 @@
         <v>0.65599999999999992</v>
       </c>
     </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B23" s="8"/>
     </row>
-    <row r="25" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B25" s="1" t="s">
         <v>57</v>
       </c>
@@ -3615,54 +3614,120 @@
       <c r="K25">
         <v>17.36</v>
       </c>
-    </row>
-    <row r="26" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="L25">
+        <v>22.81</v>
+      </c>
+    </row>
+    <row r="26" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B26" s="1" t="s">
         <v>58</v>
       </c>
       <c r="G26">
-        <v>16.61</v>
+        <v>16.82</v>
       </c>
       <c r="H26">
-        <v>18.82</v>
+        <v>19.04</v>
       </c>
       <c r="I26">
-        <v>-18.12</v>
+        <v>-17.96</v>
       </c>
       <c r="J26">
-        <v>22.56</v>
+        <v>22.81</v>
       </c>
       <c r="K26">
-        <v>17.79</v>
-      </c>
-    </row>
-    <row r="27" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B27" s="8" t="s">
+        <v>18.02</v>
+      </c>
+      <c r="L26">
+        <v>22.87</v>
+      </c>
+    </row>
+    <row r="27" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B27" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G27">
+        <v>16.25</v>
+      </c>
+      <c r="H27">
+        <v>18.54</v>
+      </c>
+      <c r="I27">
+        <v>-18.36</v>
+      </c>
+      <c r="J27">
+        <v>22.2</v>
+      </c>
+      <c r="K27">
+        <v>17.489999999999998</v>
+      </c>
+      <c r="L27">
+        <v>22.34</v>
+      </c>
+    </row>
+    <row r="28" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B28" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G27">
+      <c r="G28">
         <f>G26-G25</f>
-        <v>0.91000000000000014</v>
-      </c>
-      <c r="H27">
-        <f t="shared" ref="H27:K27" si="7">H26-H25</f>
-        <v>0.23000000000000043</v>
-      </c>
-      <c r="I27">
+        <v>1.120000000000001</v>
+      </c>
+      <c r="H28">
+        <f t="shared" ref="H28:L28" si="7">H26-H25</f>
+        <v>0.44999999999999929</v>
+      </c>
+      <c r="I28">
         <f t="shared" si="7"/>
-        <v>0.17999999999999972</v>
-      </c>
-      <c r="J27">
+        <v>0.33999999999999986</v>
+      </c>
+      <c r="J28">
         <f t="shared" si="7"/>
-        <v>0.54999999999999716</v>
-      </c>
-      <c r="K27">
+        <v>0.79999999999999716</v>
+      </c>
+      <c r="K28">
         <f t="shared" si="7"/>
-        <v>0.42999999999999972</v>
-      </c>
-      <c r="N27">
-        <f>AVERAGE(G27:K27)</f>
-        <v>0.45999999999999941</v>
+        <v>0.66000000000000014</v>
+      </c>
+      <c r="L28">
+        <f t="shared" si="7"/>
+        <v>6.0000000000002274E-2</v>
+      </c>
+      <c r="N28" s="18">
+        <f>AVERAGE(G28:L28)</f>
+        <v>0.57166666666666666</v>
+      </c>
+    </row>
+    <row r="29" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B29" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G29" s="10">
+        <f t="shared" ref="G29:L29" si="8">G25-G27</f>
+        <v>-0.55000000000000071</v>
+      </c>
+      <c r="H29" s="10">
+        <f t="shared" si="8"/>
+        <v>5.0000000000000711E-2</v>
+      </c>
+      <c r="I29" s="10">
+        <f t="shared" si="8"/>
+        <v>5.9999999999998721E-2</v>
+      </c>
+      <c r="J29" s="10">
+        <f t="shared" si="8"/>
+        <v>-0.18999999999999773</v>
+      </c>
+      <c r="K29" s="10">
+        <f t="shared" si="8"/>
+        <v>-0.12999999999999901</v>
+      </c>
+      <c r="L29" s="10">
+        <f t="shared" si="8"/>
+        <v>0.46999999999999886</v>
+      </c>
+      <c r="O29" s="11">
+        <f>AVERAGE(G29:L29)</f>
+        <v>-4.8333333333333194E-2</v>
       </c>
     </row>
   </sheetData>
